--- a/MAJSushiConfig/ig/StructureDefinition-FRLMEncounter.xlsx
+++ b/MAJSushiConfig/ig/StructureDefinition-FRLMEncounter.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMEncounter</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMEncounter</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T10:25:17+00:00</t>
+    <t>2026-09-07T11:26:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -108,7 +108,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMEntry|0.1.0</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMEntry|0.1.0</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -266,7 +266,7 @@
     <t>FRLMEncounter.header.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMPatient
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMPatient
 </t>
   </si>
   <si>
@@ -304,7 +304,7 @@
     <t>FRLMEncounter.header.author[x].authorProfessional</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMHealthProfessional
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMHealthProfessional
 </t>
   </si>
   <si>
@@ -317,7 +317,7 @@
     <t>FRLMEncounter.header.author[x].authorOrganisation</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMOrganisation
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMOrganisation
 </t>
   </si>
   <si>
@@ -330,7 +330,7 @@
     <t>FRLMEncounter.header.author[x].authorDevice</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMDevice
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMDevice
 </t>
   </si>
   <si>
@@ -343,8 +343,8 @@
     <t>FRLMEncounter.header.performer[x]</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMHealthProfessional
-https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMOrganisation</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMHealthProfessional
+https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMOrganisation</t>
   </si>
   <si>
     <t>Exécutant (performer)</t>
@@ -392,7 +392,7 @@
     <t>FRLMEncounter.header.informant</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMInformant
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMInformant
 </t>
   </si>
   <si>
@@ -451,7 +451,7 @@
     <t>FRLMEncounter.participant</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMParticipant
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMParticipant
 </t>
   </si>
   <si>
@@ -495,8 +495,8 @@
     <t>FRLMEncounter.basedOn[x]</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMCarePlan
-https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMServiceRequest</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMCarePlan
+https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMServiceRequest</t>
   </si>
   <si>
     <t>Référence à la demande ayant initié cette rencontre</t>
@@ -506,7 +506,7 @@
   </si>
   <si>
     <t>CodeableConcept
-https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMConditionhttps://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMProcedurehttps://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMObservationstring</t>
+https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMConditionhttps://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMProcedurehttps://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMObservationstring</t>
   </si>
   <si>
     <t>Motif(s) de l'admission, ex : problème, procédure ou constatation.</t>
@@ -543,7 +543,7 @@
   </si>
   <si>
     <t>CodeableConcept
-https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMCondition</t>
+https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMCondition</t>
   </si>
   <si>
     <t>Les diagnostics au moment de la sortie.</t>
@@ -567,8 +567,8 @@
     <t>FRLMEncounter.dischargeDestination.location[x]</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMOrganisation
-https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMLocation</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMOrganisation
+https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMLocation</t>
   </si>
   <si>
     <t>Le lieu ou l'organisation</t>
@@ -595,7 +595,7 @@
     <t>FRLMEncounter.subEncounter</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMEncounter
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMEncounter
 </t>
   </si>
   <si>
@@ -924,7 +924,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="221.078125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="204.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/MAJSushiConfig/ig/StructureDefinition-FRLMEncounter.xlsx
+++ b/MAJSushiConfig/ig/StructureDefinition-FRLMEncounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T11:26:50+00:00</t>
+    <t>2026-09-07T11:40:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
